--- a/static/downloads/Neverlank_TB_Import_Template.xlsx
+++ b/static/downloads/Neverlank_TB_Import_Template.xlsx
@@ -456,7 +456,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -475,11 +475,6 @@
           <t>Neverlank Chartered Accountants</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -487,12 +482,8 @@
           <t>Trial Balance Import Template</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-    </row>
+    </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -500,6 +491,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
@@ -1019,5 +1011,14 @@
     <mergeCell ref="A4:F4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;8Neverlank Chartered Accountants&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>